--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_od_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_od_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -826,7 +826,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>24-06-2021 08:30</t>
+          <t>2021-06-24 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14597,7 +14597,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15527,7 +15527,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15899,7 +15899,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -16178,7 +16178,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -16736,7 +16736,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17387,7 +17387,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18317,7 +18317,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18410,7 +18410,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19635,7 +19635,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20140,7 +20140,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="n">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21201,7 +21201,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -21771,7 +21771,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -22721,7 +22721,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>17-10-2021 08:30</t>
+          <t>2021-10-17 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -22921,7 +22921,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23107,7 +23107,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23200,7 +23200,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23293,7 +23293,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23386,7 +23386,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23665,7 +23665,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>17-10-2021 08:30</t>
+          <t>2021-10-17 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24237,7 +24237,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24330,7 +24330,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>18-04-2021 08:30</t>
+          <t>2021-04-18 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>18-04-2021 08:30</t>
+          <t>2021-04-18 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -25027,7 +25027,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25128,7 +25128,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25229,7 +25229,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="n">
@@ -25633,7 +25633,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="inlineStr"/>
@@ -25819,7 +25819,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="inlineStr"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="inlineStr"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="inlineStr"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26284,7 +26284,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26377,7 +26377,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26470,7 +26470,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26749,7 +26749,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -26842,7 +26842,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -27028,7 +27028,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -27121,7 +27121,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -27214,7 +27214,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="inlineStr"/>
@@ -27400,7 +27400,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="inlineStr"/>
@@ -27493,7 +27493,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="inlineStr"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
@@ -27683,7 +27683,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="inlineStr"/>
@@ -27780,7 +27780,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -28071,7 +28071,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -28265,7 +28265,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28362,7 +28362,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28750,7 +28750,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="n">
@@ -28849,7 +28849,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="n">
@@ -28950,7 +28950,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="n">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>17-10-2021 08:30</t>
+          <t>2021-10-17 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -29152,7 +29152,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="inlineStr"/>
@@ -29338,7 +29338,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29431,7 +29431,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29633,7 +29633,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="inlineStr"/>
@@ -29928,7 +29928,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="inlineStr"/>
@@ -30021,7 +30021,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -30114,7 +30114,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="inlineStr"/>
@@ -30207,7 +30207,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -30300,7 +30300,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30393,7 +30393,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30579,7 +30579,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30672,7 +30672,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30858,7 +30858,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -30951,7 +30951,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -31052,7 +31052,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -31153,7 +31153,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31343,7 +31343,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31438,7 +31438,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31533,7 +31533,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31628,7 +31628,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -31723,7 +31723,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="n">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="n">
@@ -32008,7 +32008,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="n">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="n">
@@ -32198,7 +32198,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="n">
@@ -32293,7 +32293,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32479,7 +32479,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="n">
@@ -32673,7 +32673,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="n">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="n">
@@ -32875,7 +32875,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="n">
@@ -32976,7 +32976,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="n">
@@ -33075,7 +33075,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="n">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="n">
@@ -33277,7 +33277,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="n">
@@ -33378,7 +33378,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="n">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="n">
@@ -33568,7 +33568,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="n">
@@ -33663,7 +33663,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="n">
@@ -33758,7 +33758,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="n">
@@ -33853,7 +33853,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="n">
@@ -33948,7 +33948,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="n">
@@ -34043,7 +34043,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>24-08-2021 08:30</t>
+          <t>2021-08-24 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -34138,7 +34138,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34328,7 +34328,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34423,7 +34423,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34518,7 +34518,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34716,7 +34716,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34817,7 +34817,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -34918,7 +34918,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -35019,7 +35019,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -35118,7 +35118,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -35219,7 +35219,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -35320,7 +35320,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -35421,7 +35421,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35522,7 +35522,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35621,7 +35621,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="n">
@@ -35722,7 +35722,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="n">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="n">
@@ -35924,7 +35924,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -36110,7 +36110,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -36203,7 +36203,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -36296,7 +36296,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36482,7 +36482,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="n">
@@ -36581,7 +36581,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="n">
@@ -36682,7 +36682,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -36775,7 +36775,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -36868,7 +36868,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="inlineStr"/>
@@ -37054,7 +37054,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="inlineStr"/>
@@ -37147,7 +37147,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="inlineStr"/>
@@ -37240,7 +37240,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="inlineStr"/>
@@ -37333,7 +37333,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="inlineStr"/>
@@ -37426,7 +37426,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="inlineStr"/>
@@ -37519,7 +37519,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="inlineStr"/>
@@ -37612,7 +37612,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="inlineStr"/>
@@ -37705,7 +37705,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="inlineStr"/>
@@ -37798,7 +37798,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37899,7 +37899,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -38000,7 +38000,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="inlineStr"/>
@@ -38093,7 +38093,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="inlineStr"/>
@@ -38186,7 +38186,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="inlineStr"/>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="inlineStr"/>
@@ -38372,7 +38372,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="inlineStr"/>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="inlineStr"/>
@@ -38558,7 +38558,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="inlineStr"/>
@@ -38651,7 +38651,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="inlineStr"/>
@@ -38744,7 +38744,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="inlineStr"/>
@@ -38837,7 +38837,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="inlineStr"/>
@@ -38930,7 +38930,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="inlineStr"/>
@@ -39023,7 +39023,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="inlineStr"/>
@@ -39116,7 +39116,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="inlineStr"/>
@@ -39209,7 +39209,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="inlineStr"/>
@@ -39302,7 +39302,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="inlineStr"/>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="inlineStr"/>
@@ -39488,7 +39488,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="inlineStr"/>
@@ -39674,7 +39674,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="inlineStr"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="inlineStr"/>
@@ -39860,7 +39860,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="inlineStr"/>
@@ -39953,7 +39953,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="inlineStr"/>
@@ -40046,7 +40046,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="inlineStr"/>
@@ -40139,7 +40139,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="inlineStr"/>
@@ -40232,7 +40232,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="n">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="n">
@@ -40434,7 +40434,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="n">
@@ -40535,7 +40535,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -40636,7 +40636,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="inlineStr"/>
@@ -40729,7 +40729,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="inlineStr"/>
@@ -40822,7 +40822,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="inlineStr"/>
@@ -40915,7 +40915,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="inlineStr"/>
@@ -41008,7 +41008,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="inlineStr"/>
@@ -41101,7 +41101,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="inlineStr"/>
@@ -41194,7 +41194,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="inlineStr"/>
@@ -41287,7 +41287,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="inlineStr"/>
@@ -41380,7 +41380,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="inlineStr"/>
@@ -41473,7 +41473,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="inlineStr"/>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="inlineStr"/>
@@ -41659,7 +41659,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="inlineStr"/>
@@ -41752,7 +41752,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="inlineStr"/>
@@ -41845,7 +41845,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="inlineStr"/>
@@ -41938,7 +41938,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="inlineStr"/>
@@ -42031,7 +42031,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="inlineStr"/>
@@ -42124,7 +42124,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -42217,7 +42217,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="inlineStr"/>
@@ -42310,7 +42310,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="inlineStr"/>
@@ -42403,7 +42403,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="inlineStr"/>
@@ -42496,7 +42496,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="inlineStr"/>
@@ -42589,7 +42589,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="inlineStr"/>
@@ -42682,7 +42682,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="inlineStr"/>
@@ -42775,7 +42775,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="inlineStr"/>
@@ -42868,7 +42868,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="n">
@@ -42969,7 +42969,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="n">
@@ -43070,7 +43070,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="inlineStr"/>
@@ -43163,7 +43163,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="inlineStr"/>
@@ -43256,7 +43256,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="inlineStr"/>
@@ -43349,7 +43349,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="inlineStr"/>
@@ -43442,7 +43442,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="inlineStr"/>
@@ -43535,7 +43535,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="inlineStr"/>
@@ -43628,7 +43628,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="inlineStr"/>
@@ -43721,7 +43721,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="inlineStr"/>
@@ -43814,7 +43814,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="inlineStr"/>
@@ -43907,7 +43907,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="inlineStr"/>
@@ -44000,7 +44000,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="inlineStr"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="inlineStr"/>
@@ -44186,7 +44186,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="inlineStr"/>
@@ -44279,7 +44279,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="inlineStr"/>
@@ -44372,7 +44372,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="inlineStr"/>
@@ -44465,7 +44465,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="inlineStr"/>
@@ -44558,7 +44558,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="inlineStr"/>
@@ -44651,7 +44651,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="inlineStr"/>
@@ -44744,7 +44744,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="inlineStr"/>
@@ -44837,7 +44837,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="inlineStr"/>
@@ -44930,7 +44930,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="inlineStr"/>
@@ -45023,7 +45023,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="inlineStr"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="inlineStr"/>
@@ -45209,7 +45209,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="inlineStr"/>
@@ -45302,7 +45302,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="inlineStr"/>
@@ -45395,7 +45395,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="inlineStr"/>
@@ -45488,7 +45488,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="inlineStr"/>
@@ -45581,7 +45581,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="inlineStr"/>
@@ -45674,7 +45674,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="inlineStr"/>
@@ -45767,7 +45767,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="inlineStr"/>
@@ -45860,7 +45860,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="inlineStr"/>
@@ -45953,7 +45953,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="inlineStr"/>
@@ -46046,7 +46046,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="inlineStr"/>
@@ -46139,7 +46139,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="inlineStr"/>
@@ -46232,7 +46232,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="inlineStr"/>
@@ -46325,7 +46325,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="inlineStr"/>
@@ -46418,7 +46418,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="n">
@@ -46519,7 +46519,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="inlineStr"/>
@@ -46612,7 +46612,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="inlineStr"/>
@@ -46705,7 +46705,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="inlineStr"/>
@@ -46798,7 +46798,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="inlineStr"/>
@@ -46891,7 +46891,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="inlineStr"/>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="inlineStr"/>
@@ -47077,7 +47077,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="inlineStr"/>
@@ -47170,7 +47170,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="inlineStr"/>
@@ -47263,7 +47263,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="inlineStr"/>
@@ -47356,7 +47356,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="n">
@@ -47457,7 +47457,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="n">
@@ -47558,7 +47558,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="inlineStr"/>
@@ -47651,7 +47651,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="inlineStr"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="inlineStr"/>
@@ -47837,7 +47837,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="inlineStr"/>
@@ -47930,7 +47930,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="inlineStr"/>
@@ -48023,7 +48023,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="inlineStr"/>
@@ -48116,7 +48116,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="n">
@@ -48211,7 +48211,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="n">
@@ -48306,7 +48306,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="n">
@@ -48401,7 +48401,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="n">
@@ -48496,7 +48496,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="n">
@@ -48591,7 +48591,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="n">
@@ -48686,7 +48686,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="n">
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="n">
@@ -48876,7 +48876,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="n">
@@ -48971,7 +48971,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="n">
@@ -49066,7 +49066,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="n">
@@ -49161,7 +49161,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="n">
@@ -49256,7 +49256,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="n">
@@ -49355,7 +49355,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="n">
@@ -49456,7 +49456,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="n">
@@ -49557,7 +49557,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="n">
@@ -49658,7 +49658,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="n">
@@ -49757,7 +49757,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="n">
@@ -49858,7 +49858,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="n">
@@ -49959,7 +49959,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="n">
@@ -50060,7 +50060,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="inlineStr"/>
@@ -50153,7 +50153,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="inlineStr"/>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="inlineStr"/>
@@ -50339,7 +50339,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="inlineStr"/>
@@ -50432,7 +50432,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="inlineStr"/>
@@ -50525,7 +50525,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="inlineStr"/>
@@ -50618,7 +50618,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="inlineStr"/>
@@ -50711,7 +50711,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="inlineStr"/>
@@ -50804,7 +50804,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="inlineStr"/>
@@ -50897,7 +50897,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="n">
@@ -50998,7 +50998,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="n">
@@ -51099,7 +51099,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="n">
@@ -51200,7 +51200,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="n">
@@ -51301,7 +51301,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="inlineStr"/>
@@ -51394,7 +51394,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="inlineStr"/>
@@ -51487,7 +51487,7 @@
       </c>
       <c r="S537" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T537" t="inlineStr"/>
@@ -51580,7 +51580,7 @@
       </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T538" t="inlineStr"/>
@@ -51673,7 +51673,7 @@
       </c>
       <c r="S539" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T539" t="inlineStr"/>
@@ -51766,7 +51766,7 @@
       </c>
       <c r="S540" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T540" t="inlineStr"/>
@@ -51859,7 +51859,7 @@
       </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T541" t="n">
@@ -51954,7 +51954,7 @@
       </c>
       <c r="S542" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T542" t="n">
@@ -52049,7 +52049,7 @@
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T543" t="n">
@@ -52144,7 +52144,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T544" t="n">
@@ -52239,7 +52239,7 @@
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T545" t="n">
@@ -52334,7 +52334,7 @@
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T546" t="n">
@@ -52429,7 +52429,7 @@
       </c>
       <c r="S547" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T547" t="n">
@@ -52524,7 +52524,7 @@
       </c>
       <c r="S548" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T548" t="n">
@@ -52619,7 +52619,7 @@
       </c>
       <c r="S549" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T549" t="n">
@@ -52714,7 +52714,7 @@
       </c>
       <c r="S550" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T550" t="n">
@@ -52809,7 +52809,7 @@
       </c>
       <c r="S551" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T551" t="n">
@@ -52904,7 +52904,7 @@
       </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T552" t="n">
@@ -52999,7 +52999,7 @@
       </c>
       <c r="S553" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T553" t="n">
@@ -53098,7 +53098,7 @@
       </c>
       <c r="S554" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T554" t="n">
@@ -53199,7 +53199,7 @@
       </c>
       <c r="S555" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T555" t="n">
@@ -53300,7 +53300,7 @@
       </c>
       <c r="S556" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T556" t="n">
@@ -53401,7 +53401,7 @@
       </c>
       <c r="S557" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T557" t="n">
@@ -53502,7 +53502,7 @@
       </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T558" t="n">
@@ -53603,7 +53603,7 @@
       </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T559" t="n">
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S560" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T560" t="n">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="S561" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T561" t="n">
@@ -53904,7 +53904,7 @@
       </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T562" t="n">
@@ -54005,7 +54005,7 @@
       </c>
       <c r="S563" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T563" t="n">
@@ -54106,7 +54106,7 @@
       </c>
       <c r="S564" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T564" t="n">
@@ -54205,7 +54205,7 @@
       </c>
       <c r="S565" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T565" t="n">
@@ -54306,7 +54306,7 @@
       </c>
       <c r="S566" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T566" t="n">
@@ -54407,7 +54407,7 @@
       </c>
       <c r="S567" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T567" t="n">
@@ -54506,7 +54506,7 @@
       </c>
       <c r="S568" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T568" t="n">
@@ -54607,7 +54607,7 @@
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T569" t="n">
@@ -54708,7 +54708,7 @@
       </c>
       <c r="S570" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T570" t="n">
@@ -54809,7 +54809,7 @@
       </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T571" t="n">
@@ -54910,7 +54910,7 @@
       </c>
       <c r="S572" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T572" t="n">
@@ -55011,7 +55011,7 @@
       </c>
       <c r="S573" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T573" t="n">
@@ -55112,7 +55112,7 @@
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T574" t="n">
@@ -55213,7 +55213,7 @@
       </c>
       <c r="S575" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T575" t="n">
@@ -55314,7 +55314,7 @@
       </c>
       <c r="S576" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T576" t="n">
@@ -55415,7 +55415,7 @@
       </c>
       <c r="S577" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T577" t="n">
@@ -55516,7 +55516,7 @@
       </c>
       <c r="S578" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T578" t="n">
@@ -55617,7 +55617,7 @@
       </c>
       <c r="S579" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T579" t="n">
@@ -55718,7 +55718,7 @@
       </c>
       <c r="S580" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T580" t="n">
@@ -55819,7 +55819,7 @@
       </c>
       <c r="S581" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T581" t="n">
@@ -55920,7 +55920,7 @@
       </c>
       <c r="S582" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T582" t="n">
@@ -56021,7 +56021,7 @@
       </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T583" t="n">
@@ -56122,7 +56122,7 @@
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T584" t="n">
@@ -56223,7 +56223,7 @@
       </c>
       <c r="S585" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T585" t="n">
@@ -56322,7 +56322,7 @@
       </c>
       <c r="S586" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T586" t="n">
@@ -56423,7 +56423,7 @@
       </c>
       <c r="S587" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T587" t="n">
@@ -56524,7 +56524,7 @@
       </c>
       <c r="S588" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T588" t="n">
@@ -56625,7 +56625,7 @@
       </c>
       <c r="S589" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T589" t="n">
@@ -56726,7 +56726,7 @@
       </c>
       <c r="S590" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T590" t="n">
@@ -56827,7 +56827,7 @@
       </c>
       <c r="S591" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T591" t="n">
@@ -56928,7 +56928,7 @@
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T592" t="n">
@@ -57029,7 +57029,7 @@
       </c>
       <c r="S593" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T593" t="n">
@@ -57130,7 +57130,7 @@
       </c>
       <c r="S594" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T594" t="n">
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S595" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T595" t="n">
@@ -57332,7 +57332,7 @@
       </c>
       <c r="S596" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T596" t="n">
@@ -57433,7 +57433,7 @@
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T597" t="n">
@@ -57534,7 +57534,7 @@
       </c>
       <c r="S598" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T598" t="n">
@@ -57635,7 +57635,7 @@
       </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T599" t="inlineStr"/>
@@ -57728,7 +57728,7 @@
       </c>
       <c r="S600" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T600" t="inlineStr"/>
@@ -57821,7 +57821,7 @@
       </c>
       <c r="S601" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T601" t="n">
@@ -57920,7 +57920,7 @@
       </c>
       <c r="S602" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T602" t="n">
@@ -58021,7 +58021,7 @@
       </c>
       <c r="S603" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T603" t="inlineStr"/>
@@ -58114,7 +58114,7 @@
       </c>
       <c r="S604" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T604" t="inlineStr"/>
@@ -58207,7 +58207,7 @@
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T605" t="inlineStr"/>
@@ -58300,7 +58300,7 @@
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T606" t="inlineStr"/>
@@ -58397,7 +58397,7 @@
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T607" t="inlineStr"/>
@@ -58494,7 +58494,7 @@
       </c>
       <c r="S608" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T608" t="inlineStr"/>
@@ -58591,7 +58591,7 @@
       </c>
       <c r="S609" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T609" t="inlineStr"/>
@@ -58688,7 +58688,7 @@
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T610" t="inlineStr"/>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S611" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T611" t="inlineStr"/>
@@ -58882,7 +58882,7 @@
       </c>
       <c r="S612" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T612" t="inlineStr"/>
@@ -58979,7 +58979,7 @@
       </c>
       <c r="S613" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T613" t="inlineStr"/>
@@ -59076,7 +59076,7 @@
       </c>
       <c r="S614" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T614" t="inlineStr"/>
@@ -59173,7 +59173,7 @@
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T615" t="inlineStr"/>
@@ -59270,7 +59270,7 @@
       </c>
       <c r="S616" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T616" t="inlineStr"/>
@@ -59367,7 +59367,7 @@
       </c>
       <c r="S617" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T617" t="inlineStr"/>
@@ -59464,7 +59464,7 @@
       </c>
       <c r="S618" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T618" t="n">
@@ -59559,7 +59559,7 @@
       </c>
       <c r="S619" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T619" t="n">
@@ -59654,7 +59654,7 @@
       </c>
       <c r="S620" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T620" t="n">
@@ -59749,7 +59749,7 @@
       </c>
       <c r="S621" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T621" t="n">
@@ -59844,7 +59844,7 @@
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T622" t="n">
@@ -59939,7 +59939,7 @@
       </c>
       <c r="S623" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T623" t="n">
@@ -60034,7 +60034,7 @@
       </c>
       <c r="S624" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T624" t="n">
@@ -60129,7 +60129,7 @@
       </c>
       <c r="S625" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T625" t="n">
@@ -60224,7 +60224,7 @@
       </c>
       <c r="S626" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T626" t="n">
@@ -60319,7 +60319,7 @@
       </c>
       <c r="S627" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T627" t="n">
@@ -60414,7 +60414,7 @@
       </c>
       <c r="S628" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T628" t="n">
@@ -60509,7 +60509,7 @@
       </c>
       <c r="S629" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T629" t="n">
@@ -60604,7 +60604,7 @@
       </c>
       <c r="S630" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T630" t="inlineStr"/>
@@ -60701,7 +60701,7 @@
       </c>
       <c r="S631" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T631" t="inlineStr"/>
@@ -60798,7 +60798,7 @@
       </c>
       <c r="S632" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T632" t="inlineStr"/>
@@ -60895,7 +60895,7 @@
       </c>
       <c r="S633" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T633" t="inlineStr"/>
@@ -60992,7 +60992,7 @@
       </c>
       <c r="S634" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T634" t="inlineStr"/>
@@ -61089,7 +61089,7 @@
       </c>
       <c r="S635" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T635" t="inlineStr"/>
@@ -61186,7 +61186,7 @@
       </c>
       <c r="S636" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T636" t="inlineStr"/>
@@ -61283,7 +61283,7 @@
       </c>
       <c r="S637" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T637" t="inlineStr"/>
@@ -61380,7 +61380,7 @@
       </c>
       <c r="S638" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T638" t="inlineStr"/>
@@ -61477,7 +61477,7 @@
       </c>
       <c r="S639" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T639" t="inlineStr"/>
@@ -61574,7 +61574,7 @@
       </c>
       <c r="S640" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T640" t="inlineStr"/>
@@ -61671,7 +61671,7 @@
       </c>
       <c r="S641" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T641" t="inlineStr"/>
@@ -61768,7 +61768,7 @@
       </c>
       <c r="S642" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T642" t="n">
@@ -61863,7 +61863,7 @@
       </c>
       <c r="S643" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T643" t="n">
@@ -61958,7 +61958,7 @@
       </c>
       <c r="S644" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T644" t="n">
@@ -62053,7 +62053,7 @@
       </c>
       <c r="S645" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T645" t="n">
@@ -62148,7 +62148,7 @@
       </c>
       <c r="S646" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T646" t="n">
@@ -62243,7 +62243,7 @@
       </c>
       <c r="S647" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T647" t="n">
@@ -62338,7 +62338,7 @@
       </c>
       <c r="S648" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T648" t="n">
@@ -62433,7 +62433,7 @@
       </c>
       <c r="S649" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T649" t="n">
@@ -62528,7 +62528,7 @@
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T650" t="n">
@@ -62623,7 +62623,7 @@
       </c>
       <c r="S651" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T651" t="n">
@@ -62718,7 +62718,7 @@
       </c>
       <c r="S652" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T652" t="n">
@@ -62813,7 +62813,7 @@
       </c>
       <c r="S653" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T653" t="n">
@@ -62908,7 +62908,7 @@
       </c>
       <c r="S654" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T654" t="n">
@@ -63003,7 +63003,7 @@
       </c>
       <c r="S655" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T655" t="n">
@@ -63098,7 +63098,7 @@
       </c>
       <c r="S656" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T656" t="n">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="S657" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T657" t="n">
@@ -63288,7 +63288,7 @@
       </c>
       <c r="S658" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T658" t="n">
@@ -63383,7 +63383,7 @@
       </c>
       <c r="S659" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T659" t="n">
@@ -63478,7 +63478,7 @@
       </c>
       <c r="S660" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T660" t="n">
@@ -63573,7 +63573,7 @@
       </c>
       <c r="S661" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T661" t="n">
@@ -63668,7 +63668,7 @@
       </c>
       <c r="S662" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T662" t="n">
@@ -63763,7 +63763,7 @@
       </c>
       <c r="S663" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T663" t="n">
@@ -63858,7 +63858,7 @@
       </c>
       <c r="S664" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T664" t="n">
@@ -63953,7 +63953,7 @@
       </c>
       <c r="S665" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T665" t="n">
@@ -64048,7 +64048,7 @@
       </c>
       <c r="S666" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T666" t="n">
@@ -64143,7 +64143,7 @@
       </c>
       <c r="S667" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T667" t="n">
@@ -64238,7 +64238,7 @@
       </c>
       <c r="S668" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T668" t="n">
@@ -64333,7 +64333,7 @@
       </c>
       <c r="S669" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T669" t="n">
@@ -64428,7 +64428,7 @@
       </c>
       <c r="S670" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T670" t="n">
@@ -64523,7 +64523,7 @@
       </c>
       <c r="S671" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T671" t="n">
@@ -64618,7 +64618,7 @@
       </c>
       <c r="S672" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T672" t="inlineStr"/>
@@ -64711,7 +64711,7 @@
       </c>
       <c r="S673" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T673" t="inlineStr"/>
@@ -64804,7 +64804,7 @@
       </c>
       <c r="S674" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T674" t="inlineStr"/>
@@ -64897,7 +64897,7 @@
       </c>
       <c r="S675" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T675" t="n">
@@ -64996,7 +64996,7 @@
       </c>
       <c r="S676" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T676" t="n">
@@ -65097,7 +65097,7 @@
       </c>
       <c r="S677" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T677" t="n">
@@ -65192,7 +65192,7 @@
       </c>
       <c r="S678" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T678" t="n">
@@ -65287,7 +65287,7 @@
       </c>
       <c r="S679" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T679" t="n">
@@ -65382,7 +65382,7 @@
       </c>
       <c r="S680" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T680" t="n">
@@ -65477,7 +65477,7 @@
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T681" t="n">
@@ -65572,7 +65572,7 @@
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T682" t="n">
@@ -65667,7 +65667,7 @@
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T683" t="n">
@@ -65762,7 +65762,7 @@
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T684" t="n">
@@ -65857,7 +65857,7 @@
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T685" t="n">
@@ -65952,7 +65952,7 @@
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T686" t="n">
@@ -66047,7 +66047,7 @@
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T687" t="n">
@@ -66142,7 +66142,7 @@
       </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T688" t="n">
@@ -66237,7 +66237,7 @@
       </c>
       <c r="S689" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T689" t="n">
@@ -66338,7 +66338,7 @@
       </c>
       <c r="S690" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T690" t="n">
@@ -66439,7 +66439,7 @@
       </c>
       <c r="S691" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T691" t="inlineStr"/>
@@ -66532,7 +66532,7 @@
       </c>
       <c r="S692" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T692" t="inlineStr"/>
@@ -66625,7 +66625,7 @@
       </c>
       <c r="S693" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T693" t="inlineStr"/>
@@ -66718,7 +66718,7 @@
       </c>
       <c r="S694" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T694" t="inlineStr"/>
@@ -66811,7 +66811,7 @@
       </c>
       <c r="S695" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T695" t="inlineStr"/>
@@ -66904,7 +66904,7 @@
       </c>
       <c r="S696" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T696" t="inlineStr"/>
@@ -66997,7 +66997,7 @@
       </c>
       <c r="S697" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T697" t="inlineStr"/>
@@ -67090,7 +67090,7 @@
       </c>
       <c r="S698" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T698" t="inlineStr"/>
@@ -67183,7 +67183,7 @@
       </c>
       <c r="S699" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T699" t="inlineStr"/>
@@ -67276,7 +67276,7 @@
       </c>
       <c r="S700" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T700" t="inlineStr"/>
@@ -67369,7 +67369,7 @@
       </c>
       <c r="S701" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T701" t="inlineStr"/>
@@ -67462,7 +67462,7 @@
       </c>
       <c r="S702" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T702" t="inlineStr"/>
@@ -67555,7 +67555,7 @@
       </c>
       <c r="S703" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T703" t="inlineStr"/>
@@ -67648,7 +67648,7 @@
       </c>
       <c r="S704" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T704" t="inlineStr"/>
@@ -67741,7 +67741,7 @@
       </c>
       <c r="S705" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T705" t="inlineStr"/>
@@ -67834,7 +67834,7 @@
       </c>
       <c r="S706" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T706" t="inlineStr"/>
@@ -67927,7 +67927,7 @@
       </c>
       <c r="S707" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T707" t="inlineStr"/>
@@ -68020,7 +68020,7 @@
       </c>
       <c r="S708" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T708" t="inlineStr"/>
@@ -68113,7 +68113,7 @@
       </c>
       <c r="S709" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T709" t="n">
@@ -68212,7 +68212,7 @@
       </c>
       <c r="S710" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T710" t="n">
@@ -68313,7 +68313,7 @@
       </c>
       <c r="S711" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T711" t="inlineStr"/>
@@ -68406,7 +68406,7 @@
       </c>
       <c r="S712" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T712" t="inlineStr"/>
@@ -68499,7 +68499,7 @@
       </c>
       <c r="S713" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T713" t="inlineStr"/>
@@ -68592,7 +68592,7 @@
       </c>
       <c r="S714" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T714" t="inlineStr"/>
@@ -68685,7 +68685,7 @@
       </c>
       <c r="S715" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T715" t="inlineStr"/>
@@ -68778,7 +68778,7 @@
       </c>
       <c r="S716" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T716" t="inlineStr"/>
@@ -68871,7 +68871,7 @@
       </c>
       <c r="S717" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T717" t="inlineStr"/>
@@ -68964,7 +68964,7 @@
       </c>
       <c r="S718" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T718" t="inlineStr"/>
@@ -69057,7 +69057,7 @@
       </c>
       <c r="S719" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T719" t="inlineStr"/>
@@ -69150,7 +69150,7 @@
       </c>
       <c r="S720" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T720" t="inlineStr"/>
@@ -69243,7 +69243,7 @@
       </c>
       <c r="S721" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T721" t="inlineStr"/>
@@ -69336,7 +69336,7 @@
       </c>
       <c r="S722" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T722" t="inlineStr"/>
@@ -69429,7 +69429,7 @@
       </c>
       <c r="S723" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T723" t="inlineStr"/>
@@ -69522,7 +69522,7 @@
       </c>
       <c r="S724" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T724" t="inlineStr"/>
@@ -69615,7 +69615,7 @@
       </c>
       <c r="S725" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T725" t="inlineStr"/>
@@ -69708,7 +69708,7 @@
       </c>
       <c r="S726" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T726" t="inlineStr"/>
@@ -69801,7 +69801,7 @@
       </c>
       <c r="S727" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T727" t="inlineStr"/>
@@ -69894,7 +69894,7 @@
       </c>
       <c r="S728" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T728" t="inlineStr"/>
@@ -69987,7 +69987,7 @@
       </c>
       <c r="S729" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T729" t="inlineStr"/>
@@ -70080,7 +70080,7 @@
       </c>
       <c r="S730" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T730" t="inlineStr"/>
@@ -70173,7 +70173,7 @@
       </c>
       <c r="S731" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T731" t="inlineStr"/>
@@ -70266,7 +70266,7 @@
       </c>
       <c r="S732" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T732" t="inlineStr"/>
@@ -70359,7 +70359,7 @@
       </c>
       <c r="S733" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T733" t="inlineStr"/>
@@ -70452,7 +70452,7 @@
       </c>
       <c r="S734" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T734" t="inlineStr"/>
@@ -70545,7 +70545,7 @@
       </c>
       <c r="S735" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T735" t="inlineStr"/>
@@ -70638,7 +70638,7 @@
       </c>
       <c r="S736" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T736" t="inlineStr"/>
@@ -70731,7 +70731,7 @@
       </c>
       <c r="S737" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T737" t="inlineStr"/>
@@ -70824,7 +70824,7 @@
       </c>
       <c r="S738" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T738" t="inlineStr"/>
@@ -70917,7 +70917,7 @@
       </c>
       <c r="S739" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T739" t="inlineStr"/>
@@ -71010,7 +71010,7 @@
       </c>
       <c r="S740" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T740" t="inlineStr"/>
@@ -71103,7 +71103,7 @@
       </c>
       <c r="S741" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T741" t="n">
@@ -71202,7 +71202,7 @@
       </c>
       <c r="S742" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T742" t="n">
@@ -71303,7 +71303,7 @@
       </c>
       <c r="S743" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T743" t="inlineStr"/>
@@ -71396,7 +71396,7 @@
       </c>
       <c r="S744" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T744" t="inlineStr"/>
@@ -71489,7 +71489,7 @@
       </c>
       <c r="S745" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T745" t="inlineStr"/>
@@ -71582,7 +71582,7 @@
       </c>
       <c r="S746" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T746" t="inlineStr"/>
@@ -71675,7 +71675,7 @@
       </c>
       <c r="S747" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T747" t="inlineStr"/>
@@ -71768,7 +71768,7 @@
       </c>
       <c r="S748" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T748" t="inlineStr"/>
@@ -71861,7 +71861,7 @@
       </c>
       <c r="S749" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T749" t="inlineStr"/>
@@ -71954,7 +71954,7 @@
       </c>
       <c r="S750" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T750" t="inlineStr"/>
@@ -72047,7 +72047,7 @@
       </c>
       <c r="S751" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T751" t="inlineStr"/>
@@ -72140,7 +72140,7 @@
       </c>
       <c r="S752" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T752" t="n">
@@ -72239,7 +72239,7 @@
       </c>
       <c r="S753" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T753" t="n">
@@ -72340,7 +72340,7 @@
       </c>
       <c r="S754" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T754" t="n">
@@ -72441,7 +72441,7 @@
       </c>
       <c r="S755" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T755" t="n">
@@ -72542,7 +72542,7 @@
       </c>
       <c r="S756" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T756" t="inlineStr"/>
@@ -72635,7 +72635,7 @@
       </c>
       <c r="S757" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T757" t="inlineStr"/>
@@ -72728,7 +72728,7 @@
       </c>
       <c r="S758" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T758" t="inlineStr"/>
@@ -72821,7 +72821,7 @@
       </c>
       <c r="S759" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T759" t="inlineStr"/>
@@ -72914,7 +72914,7 @@
       </c>
       <c r="S760" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T760" t="inlineStr"/>
@@ -73007,7 +73007,7 @@
       </c>
       <c r="S761" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T761" t="inlineStr"/>
@@ -73100,7 +73100,7 @@
       </c>
       <c r="S762" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T762" t="n">
@@ -73199,7 +73199,7 @@
       </c>
       <c r="S763" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T763" t="n">
@@ -73300,7 +73300,7 @@
       </c>
       <c r="S764" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T764" t="inlineStr"/>
@@ -73393,7 +73393,7 @@
       </c>
       <c r="S765" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T765" t="inlineStr"/>
@@ -73486,7 +73486,7 @@
       </c>
       <c r="S766" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T766" t="inlineStr"/>
@@ -73579,7 +73579,7 @@
       </c>
       <c r="S767" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T767" t="inlineStr"/>
@@ -73672,7 +73672,7 @@
       </c>
       <c r="S768" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T768" t="inlineStr"/>
@@ -73765,7 +73765,7 @@
       </c>
       <c r="S769" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T769" t="inlineStr"/>
@@ -73858,7 +73858,7 @@
       </c>
       <c r="S770" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T770" t="inlineStr"/>
@@ -73951,7 +73951,7 @@
       </c>
       <c r="S771" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T771" t="inlineStr"/>
@@ -74044,7 +74044,7 @@
       </c>
       <c r="S772" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T772" t="inlineStr"/>
@@ -74137,7 +74137,7 @@
       </c>
       <c r="S773" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T773" t="inlineStr"/>
@@ -74230,7 +74230,7 @@
       </c>
       <c r="S774" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T774" t="inlineStr"/>
@@ -74323,7 +74323,7 @@
       </c>
       <c r="S775" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T775" t="n">
@@ -74418,7 +74418,7 @@
       </c>
       <c r="S776" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T776" t="n">
@@ -74513,7 +74513,7 @@
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T777" t="n">
@@ -74608,7 +74608,7 @@
       </c>
       <c r="S778" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T778" t="n">
@@ -74703,7 +74703,7 @@
       </c>
       <c r="S779" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T779" t="n">
@@ -74798,7 +74798,7 @@
       </c>
       <c r="S780" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T780" t="n">
@@ -74893,7 +74893,7 @@
       </c>
       <c r="S781" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T781" t="n">
@@ -74988,7 +74988,7 @@
       </c>
       <c r="S782" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T782" t="n">
@@ -75083,7 +75083,7 @@
       </c>
       <c r="S783" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T783" t="n">
@@ -75178,7 +75178,7 @@
       </c>
       <c r="S784" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T784" t="n">
@@ -75273,7 +75273,7 @@
       </c>
       <c r="S785" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T785" t="n">
@@ -75368,7 +75368,7 @@
       </c>
       <c r="S786" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T786" t="n">
@@ -75463,7 +75463,7 @@
       </c>
       <c r="S787" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T787" t="n">
@@ -75558,7 +75558,7 @@
       </c>
       <c r="S788" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T788" t="n">
@@ -75653,7 +75653,7 @@
       </c>
       <c r="S789" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T789" t="n">
@@ -75748,7 +75748,7 @@
       </c>
       <c r="S790" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T790" t="n">
@@ -75843,7 +75843,7 @@
       </c>
       <c r="S791" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T791" t="n">
@@ -75938,7 +75938,7 @@
       </c>
       <c r="S792" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T792" t="n">
@@ -76033,7 +76033,7 @@
       </c>
       <c r="S793" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T793" t="n">
@@ -76128,7 +76128,7 @@
       </c>
       <c r="S794" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T794" t="n">
@@ -76223,7 +76223,7 @@
       </c>
       <c r="S795" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T795" t="n">
@@ -76318,7 +76318,7 @@
       </c>
       <c r="S796" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T796" t="n">
@@ -76413,7 +76413,7 @@
       </c>
       <c r="S797" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T797" t="n">
@@ -76508,7 +76508,7 @@
       </c>
       <c r="S798" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T798" t="n">
@@ -76603,7 +76603,7 @@
       </c>
       <c r="S799" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T799" t="n">
@@ -76698,7 +76698,7 @@
       </c>
       <c r="S800" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T800" t="n">
@@ -76793,7 +76793,7 @@
       </c>
       <c r="S801" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T801" t="n">
@@ -76888,7 +76888,7 @@
       </c>
       <c r="S802" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T802" t="n">
@@ -76983,7 +76983,7 @@
       </c>
       <c r="S803" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T803" t="n">
@@ -77078,7 +77078,7 @@
       </c>
       <c r="S804" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T804" t="n">
@@ -77173,7 +77173,7 @@
       </c>
       <c r="S805" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T805" t="n">
@@ -77268,7 +77268,7 @@
       </c>
       <c r="S806" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T806" t="n">
@@ -77363,7 +77363,7 @@
       </c>
       <c r="S807" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T807" t="n">
@@ -77458,7 +77458,7 @@
       </c>
       <c r="S808" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T808" t="n">
@@ -77553,7 +77553,7 @@
       </c>
       <c r="S809" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T809" t="n">
@@ -77648,7 +77648,7 @@
       </c>
       <c r="S810" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T810" t="n">
@@ -77743,7 +77743,7 @@
       </c>
       <c r="S811" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T811" t="n">
@@ -77838,7 +77838,7 @@
       </c>
       <c r="S812" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T812" t="n">
@@ -77933,7 +77933,7 @@
       </c>
       <c r="S813" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T813" t="n">
@@ -78028,7 +78028,7 @@
       </c>
       <c r="S814" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T814" t="n">
@@ -78123,7 +78123,7 @@
       </c>
       <c r="S815" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T815" t="n">
@@ -78218,7 +78218,7 @@
       </c>
       <c r="S816" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T816" t="n">
@@ -78313,7 +78313,7 @@
       </c>
       <c r="S817" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T817" t="n">
@@ -78408,7 +78408,7 @@
       </c>
       <c r="S818" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T818" t="n">
@@ -78503,7 +78503,7 @@
       </c>
       <c r="S819" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T819" t="n">
@@ -78604,7 +78604,7 @@
       </c>
       <c r="S820" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T820" t="n">
@@ -78705,7 +78705,7 @@
       </c>
       <c r="S821" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T821" t="n">
@@ -78806,7 +78806,7 @@
       </c>
       <c r="S822" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T822" t="n">
@@ -78905,7 +78905,7 @@
       </c>
       <c r="S823" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T823" t="n">
@@ -79000,7 +79000,7 @@
       </c>
       <c r="S824" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T824" t="n">
@@ -79095,7 +79095,7 @@
       </c>
       <c r="S825" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T825" t="n">
@@ -79190,7 +79190,7 @@
       </c>
       <c r="S826" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T826" t="n">
@@ -79285,7 +79285,7 @@
       </c>
       <c r="S827" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T827" t="n">
@@ -79380,7 +79380,7 @@
       </c>
       <c r="S828" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T828" t="n">
@@ -79475,7 +79475,7 @@
       </c>
       <c r="S829" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T829" t="n">
@@ -79570,7 +79570,7 @@
       </c>
       <c r="S830" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T830" t="n">
@@ -79665,7 +79665,7 @@
       </c>
       <c r="S831" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T831" t="n">
@@ -79760,7 +79760,7 @@
       </c>
       <c r="S832" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T832" t="n">
@@ -79855,7 +79855,7 @@
       </c>
       <c r="S833" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T833" t="n">
@@ -79950,7 +79950,7 @@
       </c>
       <c r="S834" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T834" t="n">
@@ -80045,7 +80045,7 @@
       </c>
       <c r="S835" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T835" t="n">
@@ -80146,7 +80146,7 @@
       </c>
       <c r="S836" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T836" t="n">
@@ -80247,7 +80247,7 @@
       </c>
       <c r="S837" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T837" t="n">
@@ -80346,7 +80346,7 @@
       </c>
       <c r="S838" t="inlineStr">
         <is>
-          <t>17-10-2021 08:30</t>
+          <t>2021-10-17 08:30:00</t>
         </is>
       </c>
       <c r="T838" t="n">
@@ -80447,7 +80447,7 @@
       </c>
       <c r="S839" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T839" t="n">
@@ -80546,7 +80546,7 @@
       </c>
       <c r="S840" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T840" t="n">
@@ -80647,7 +80647,7 @@
       </c>
       <c r="S841" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T841" t="inlineStr"/>
@@ -80740,7 +80740,7 @@
       </c>
       <c r="S842" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T842" t="inlineStr"/>
@@ -80833,7 +80833,7 @@
       </c>
       <c r="S843" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T843" t="inlineStr"/>
@@ -80926,7 +80926,7 @@
       </c>
       <c r="S844" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T844" t="inlineStr"/>
@@ -81019,7 +81019,7 @@
       </c>
       <c r="S845" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T845" t="inlineStr"/>
@@ -81112,7 +81112,7 @@
       </c>
       <c r="S846" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T846" t="inlineStr"/>
@@ -81205,7 +81205,7 @@
       </c>
       <c r="S847" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T847" t="n">
@@ -81304,7 +81304,7 @@
       </c>
       <c r="S848" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T848" t="n">
@@ -81405,7 +81405,7 @@
       </c>
       <c r="S849" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T849" t="n">
@@ -81506,7 +81506,7 @@
       </c>
       <c r="S850" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T850" t="n">
@@ -81607,7 +81607,7 @@
       </c>
       <c r="S851" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T851" t="inlineStr"/>
@@ -81700,7 +81700,7 @@
       </c>
       <c r="S852" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T852" t="inlineStr"/>
@@ -81793,7 +81793,7 @@
       </c>
       <c r="S853" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T853" t="inlineStr"/>
@@ -81886,7 +81886,7 @@
       </c>
       <c r="S854" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T854" t="inlineStr"/>
@@ -81979,7 +81979,7 @@
       </c>
       <c r="S855" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T855" t="inlineStr"/>
@@ -82072,7 +82072,7 @@
       </c>
       <c r="S856" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T856" t="inlineStr"/>
@@ -82165,7 +82165,7 @@
       </c>
       <c r="S857" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T857" t="inlineStr"/>
@@ -82258,7 +82258,7 @@
       </c>
       <c r="S858" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T858" t="inlineStr"/>
@@ -82351,7 +82351,7 @@
       </c>
       <c r="S859" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T859" t="inlineStr"/>
@@ -82444,7 +82444,7 @@
       </c>
       <c r="S860" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T860" t="n">
@@ -82545,7 +82545,7 @@
       </c>
       <c r="S861" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T861" t="n">
